--- a/workbooks/Kamu_Diplomasisi_Ogrenme_Atolyesi_TR.xlsx
+++ b/workbooks/Kamu_Diplomasisi_Ogrenme_Atolyesi_TR.xlsx
@@ -12,6 +12,7 @@
     <sheet name="2 Kanıt Çalışması" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="3 Ölçüm Deneyi" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="4 Kavram Rehberi" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="5 Araştırma Tasarımı" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="268">
   <si>
     <t xml:space="preserve">Kamu diplomasisi: ilk adımlar</t>
   </si>
@@ -689,6 +690,144 @@
   </si>
   <si>
     <t xml:space="preserve">Kaynak: Dersin Türkçe notlarındaki kavramsal açıklamalar. Günlük benzetmeler yalnızca öğrenmeyi kolaylaştıran örneklerdir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Araştırma tasarımınızı adım adım kurun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Çözülmüş kurmaca örneği okuyun. 2. Sarı sütuna kendi vakanızı yazın. 3. İddianızı desteklemeyen kanıtı da arayın.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaynak kökeni, belgenin kim tarafından, ne zaman ve hangi amaçla üretildiğini ve size nasıl ulaştığını belirtir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gözlem belgede bulunan şeydir. Yorum, bundan çıkardığınız anlamdır. İkisini ayrı yazmak çıkarımınızı denetlenebilir kılar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Örnek tamamen kurmacadır. ÖRNEK-1 gerçek bir belge kodu değildir. Sarı alanlara öğrenci adı veya kişisel veri yazmayın.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kanıtı sorgulama alanı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Çözülmüş kurmaca örnek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sizin çalışmanız (doldurun)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İddia: Sınadığım cümle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Değişim atölyesi, iki öğretmenin ilk ortak ders planını hazırlamasına katkıda bulundu. Bu, sınanacak iddiadır; henüz sonuç değildir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaynak kökeni: Belgeyi kim üretti?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ÖRNEK-1: Katılımcı A’nın katılımcı B’ye atölye sonrasında yazdığı varsayılan özel mektup. Üretici, alıcı, tarih, amaç ve saklandığı yer gerçek araştırmada ayrıca doğrulanır.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gözlem: Belgede tam olarak ne var?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varsayılan mektup, ortak bir ders taslağından söz eder. Bu gözlem, mektubun içeriğine ilişkindir; taslağın uygulandığını göstermez.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yorum: Bu gözlemden ne çıkarıyorum?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atölye sonrasında iletişimin sürmüş olmasıyla uyumludur. Atölyenin tek neden olduğu veya ilişkinin kalıcı olduğu sonucuna yetmez.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rakip açıklama: Başka neden olabilir mi?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Öğretmenler önceden tanışıyor veya başka bir proje için zaten işbirliği planlıyor olabilir. Atölye öncesi yazışmalar bu açıklamayı sınayabilir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sınırlılık: Kanıtımın sınırı nedir?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tek bir öz bildirime dayanır. Yazışmanın seçilerek korunması, olumlu anlatım ve karşı tarafın sessizliği sonucu çarpıtabilir. İletişim, politika değişikliği anlamına gelmez.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonraki kanıt: Neyi kontrol edeceğim?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atölye öncesi kayıtları, ikinci katılımcının anlatısını ve tarihli ortak taslağı karşılaştırırım. Çelişki bulursam iddiayı daraltırım; aynı kaynağın tekrarını bağımsız doğrulama saymam.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Şimdi tasarım kararları: Her satır bir araştırma tercihini açık eder. Veri yoksa sonuç uydurmak yerine hangi veriyi arayacağınızı yazın.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tasarım kararı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Örnekte nasıl uygulanır?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benim araştırma planım</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Araştırma sorusu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atölye, belirli iki öğretmenin ilk ortak ders taslağını hazırlamasına hangi süreçle katkıda bulundu?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İnceleme birimi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bir öğretmen çifti ve onun ortak çalışma süreci. Kişi, etkinlik ve ülke düzeyindeki iddiaları birbirine karıştırmam.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zaman ve kapsam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varsayımsal plan: atölyeden önceki ve sonraki üç ay. Bu sınırın dışındaki olayları ancak gerekçesini belirterek eklerim.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beklenen mekanizma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atölyede temas kurulması, ortak bir konu seçilmesi ve birlikte taslak hazırlanması. Her adım için ayrı bir iz ararım.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gösterge ve tanımı</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarih ve ortak katkı izi bulunan ders taslağı. Katılım listesi yalnız katılımı gösterir; ortak üretimin yerine geçmez.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaka seçimi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yalnız başarı anlatılarını seçmem. Devam etmeyen temasları da arar, hangi kişilerin veya belgelerin neden dışarıda kaldığını kaydederim.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karşılaştırma ve karşı olgu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atölye öncesindeki işbirliğini ve uygun benzer katılmayan kişileri araştırırım. Grupların başlangıçta farklı olabileceğini açıklarım; benzerliği otomatik varsaymam.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Etik ve veri yönetimi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gönüllü katılım, uygun izin, kişisel bilgilerin azaltılması ve güvenli saklama planı kurarım. Öğrenci verilerini bu çalışma kitabına kopyalamam.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaynak gösterme ve denetim izi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yazar, tarih, başlık, koleksiyon veya yayın, kayıt/sayfa ve erişim bilgisini kaydederim. Çeviri, eksik belge ve değişen yorum için kısa bir işlem günlüğü tutarım.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teslim öncesi: İddia, gözlem, yorum ve sınır ayrı mı? En güçlü rakip açıklamayı sınamak için hangi kanıt gerekiyor?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ders dayanağı: 6. hafta değişimler, 14. hafta kanıt ve değerlendirme. Kurmaca örnek herhangi bir tarihsel sonuca kanıt oluşturmaz.</t>
   </si>
 </sst>
 </file>
@@ -1348,11 +1487,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="96920239"/>
-        <c:axId val="79127438"/>
+        <c:axId val="73527653"/>
+        <c:axId val="48016607"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="96920239"/>
+        <c:axId val="73527653"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1397,7 +1536,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79127438"/>
+        <c:crossAx val="48016607"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1405,7 +1544,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="79127438"/>
+        <c:axId val="48016607"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1450,7 +1589,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96920239"/>
+        <c:crossAx val="73527653"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4172,4 +4311,380 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF801C35"/>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E36"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="59.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="2.67"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
+      <c r="B2" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1"/>
+      <c r="B9" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1"/>
+      <c r="B10" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D10" s="8"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1"/>
+      <c r="B11" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1"/>
+      <c r="B12" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1"/>
+      <c r="B13" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1"/>
+      <c r="B14" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D14" s="12"/>
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1"/>
+      <c r="B15" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="D15" s="12"/>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1"/>
+      <c r="B16" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="D16" s="16"/>
+      <c r="E16" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+    </row>
+    <row r="19" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1"/>
+      <c r="B20" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1"/>
+      <c r="B21" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1"/>
+      <c r="B22" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="D22" s="12"/>
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1"/>
+      <c r="B23" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="D23" s="12"/>
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1"/>
+      <c r="B24" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1"/>
+      <c r="B25" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1"/>
+      <c r="B26" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="D26" s="12"/>
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1"/>
+      <c r="B27" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="D27" s="12"/>
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1"/>
+      <c r="B28" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="D28" s="12"/>
+      <c r="E28" s="1"/>
+    </row>
+    <row r="29" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1"/>
+      <c r="B29" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="D29" s="16"/>
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1"/>
+      <c r="B34" s="25" t="str">
+        <f aca="false">HYPERLINK("https://mayhewforever.github.io/kamudiplomasisi/notes/Hafta_06_Ders_Notu_TR.html","6. hafta: değişimler")</f>
+        <v>6. hafta: değişimler</v>
+      </c>
+      <c r="C34" s="25" t="str">
+        <f aca="false">HYPERLINK("https://mayhewforever.github.io/kamudiplomasisi/notes/Hafta_14_Ders_Notu_TR.html","14. hafta: ölçüm")</f>
+        <v>14. hafta: ölçüm</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" customFormat="false" ht="25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/workbooks/Kamu_Diplomasisi_Ogrenme_Atolyesi_TR.xlsx
+++ b/workbooks/Kamu_Diplomasisi_Ogrenme_Atolyesi_TR.xlsx
@@ -24,24 +24,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="268">
-  <si>
-    <t xml:space="preserve">Kamu diplomasisi: ilk adımlar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Bu hafta hangi konuyu işliyorsanız o satırı bulun. “Ders notunu aç” bağlantısına tıklayın.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. “Küçük görev” sütununu uygulayın. “Yazacağınız sonuç” kadar kısa bir cevap hazırlayın.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Sarı durum hücresinden seçin. Sonra 2. sayfadaki örneği okuyup kendi kanıt satırınızı doldurun.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gündelik benzetme: Bir afişi görmek, afişte önerilen ürünü beğenmek veya satın almakla aynı şey değildir.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Excel ipucu: Sarı hücreye tıklayın, yazın ve Enter’a basın. Diğer sayfalara alttaki sekmelerden geçin.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="267">
+  <si>
+    <t xml:space="preserve">Kamu diplomasisi: haftalık çalışma rehberi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. İlgili haftanın satırını belirleyiniz. “Ders notunu aç” bağlantısından haftalık okuma metnine ulaşınız.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. “Uygulama” sütunundaki çalışmayı tamamlayınız. “Beklenen çıktı” sütununda belirtilen kapsamda kısa bir yanıt hazırlayınız.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Sarı hücrede çalışma durumunu seçiniz. Ardından 2. sayfadaki örneği inceleyerek kanıt tablosunda bir satır doldurunuz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Açıklayıcı benzetme: Bir afişle karşılaşılması, tanıtılan ürünün beğenildiğini veya satın alındığını tek başına göstermez.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Çalışma kitabının kullanımı: Sarı hücreyi seçip veriyi giriniz ve Enter’a basınız. Sayfalar arasında alt sekmelerden geçiş yapınız.</t>
   </si>
   <si>
     <t xml:space="preserve">Hafta</t>
@@ -50,25 +50,25 @@
     <t xml:space="preserve">Konu</t>
   </si>
   <si>
-    <t xml:space="preserve">Küçük görev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yazacağınız sonuç</t>
+    <t xml:space="preserve">Uygulama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beklenen çıktı</t>
   </si>
   <si>
     <t xml:space="preserve">Ders notu</t>
   </si>
   <si>
-    <t xml:space="preserve">Durum (siz seçin)</t>
+    <t xml:space="preserve">Çalışma durumu</t>
   </si>
   <si>
     <t xml:space="preserve">Güç türlerini ayırmak</t>
   </si>
   <si>
-    <t xml:space="preserve">Bir burs örneği seçin. Para, çekicilik ve beklenen sonucu ayrı yazın.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Üç cümle: kaynak ne, araç ne, sonuç için hangi kanıt eksik?</t>
+    <t xml:space="preserve">Bir burs örneği seçiniz. Finansman kaynağını, çekiciliği ve beklenen sonucu ayrı ayrı belirtiniz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Üç cümlede kaynağı, aracı ve sonucu değerlendirmek için gereken ek kanıtı belirtiniz.</t>
   </si>
   <si>
     <t xml:space="preserve">Başlamadım</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">Franklin ve Fransa</t>
   </si>
   <si>
-    <t xml:space="preserve">Franklin’in bir bilim veya toplum ağı temasını seçin. Teması, ittifak kararından ayırın.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">İki neden: temasın katkısı ne olabilir, kararın başka nedeni ne olabilir?</t>
+    <t xml:space="preserve">Franklin’in bilimsel veya toplumsal ağlardaki bir temasını seçiniz. Bu teması ittifak kararından analitik olarak ayırınız.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temasın olası katkısına ve kararı açıklayabilecek başka bir nedene ilişkin iki açıklama.</t>
   </si>
   <si>
     <t xml:space="preserve">Birlik ve Avrupa</t>
   </si>
   <si>
-    <t xml:space="preserve">Birlik yönetiminin bir anlatısını bulun. Avrupa’daki hangi kitleye seslendiğini yazın.</t>
+    <t xml:space="preserve">Birlik yönetiminin kullandığı bir anlatıyı belirleyiniz. Avrupa’da yöneldiği hedef kitleyi açıklayınız.</t>
   </si>
   <si>
     <t xml:space="preserve">Bir mesaj, bir kitle, mesajın nasıl karşılandığını gösterecek bir belge türü.</t>
@@ -95,34 +95,34 @@
     <t xml:space="preserve">Konfederasyon ve pamuk</t>
   </si>
   <si>
-    <t xml:space="preserve">Pamuk kaynağının neden otomatik siyasi destek üretmediğini açıklayın.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bir kaynak, bir beklenen sonuç, zinciri bozabilecek iki koşul.</t>
+    <t xml:space="preserve">Pamuk kaynağının neden kendiliğinden siyasi desteğe dönüşmediğini açıklayınız.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bir kaynak, bir beklenen sonuç ve öngörülen süreci kesintiye uğratabilecek iki koşul.</t>
   </si>
   <si>
     <t xml:space="preserve">Küba ve insani yardım</t>
   </si>
   <si>
-    <t xml:space="preserve">Yardım faaliyeti ile yardımın medyada anlatılmasını ayrı düşünün.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Faaliyet için bir kanıt, habercilik için bir kanıt, etki için bir eksik kanıt.</t>
+    <t xml:space="preserve">Yardım faaliyetini, bu faaliyetin medyadaki temsilinden ayırarak inceleyiniz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faaliyete ve haberciliğe ilişkin birer kanıt ile etkiyi değerlendirmek için gereken ek kanıt.</t>
   </si>
   <si>
     <t xml:space="preserve">Eğitim değişimleri</t>
   </si>
   <si>
-    <t xml:space="preserve">Bir öğrenci değişim programında ev sahibi ile katılımcının ne öğrendiğini yazın.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Katılım sayısının yanında izleyeceğiniz bir ilişki göstergesi.</t>
+    <t xml:space="preserve">Bir öğrenci değişim programında ev sahibi ile katılımcının öğrenme deneyimlerini ayrı ayrı açıklayınız.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katılım sayısına ek olarak izlenebilecek bir ilişki göstergesi.</t>
   </si>
   <si>
     <t xml:space="preserve">CPI ve iletişim ağı</t>
   </si>
   <si>
-    <t xml:space="preserve">Kamuoyu Bilgilendirme Komitesini (CPI) merkez, aracı ve kitle olarak üç kutuya ayırın.</t>
+    <t xml:space="preserve">Kamuoyu Bilgilendirme Komitesinin (CPI) iletişim ağını merkez, aracı ve kitle başlıklarıyla üç kutuda gösteriniz.</t>
   </si>
   <si>
     <t xml:space="preserve">Bir afişin üretilmesi ile bir kişinin ikna olması arasındaki eksik adım.</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">Propaganda ve etik</t>
   </si>
   <si>
-    <t xml:space="preserve">Doğru bilgiler içeren ama kaynağı gizli bir mesajı değerlendirin.</t>
+    <t xml:space="preserve">Doğru bilgiler içeren ancak kaynağı açıklanmayan bir mesajı değerlendiriniz.</t>
   </si>
   <si>
     <t xml:space="preserve">Kaynak, eksik bağlam ve düzeltme yolu hakkında üç soru.</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">Vakıflar ve özel ağlar</t>
   </si>
   <si>
-    <t xml:space="preserve">Bir vakıf veya üniversite örneği seçin. Kimin finansman verdiğini ve kararı kimin aldığını ayırın.</t>
+    <t xml:space="preserve">Bir vakıf veya üniversite örneği seçiniz. Finansman sağlayan aktörlerle karar alan aktörleri ayırınız.</t>
   </si>
   <si>
     <t xml:space="preserve">İki aktör ve birbirlerinden bağımsız olabilecekleri bir nokta.</t>
@@ -149,25 +149,25 @@
     <t xml:space="preserve">Savaş dönemi kurumları</t>
   </si>
   <si>
-    <t xml:space="preserve">Notta tanıtılan üç kurumu amaç, hedef insanlar ve kullanılan araç başlıklarında karşılaştırın.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Üç kısa satır. Aynı aracı kullanmanın neden aynı görev olmadığını ekleyin.</t>
+    <t xml:space="preserve">Ders notundaki üç kurumu amaç, hedef kamu ve kullanılan araç bakımından karşılaştırınız.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Üç kısa karşılaştırma satırı. Aynı aracın kullanılmasının neden aynı kurumsal göreve işaret etmediğini açıklayınız.</t>
   </si>
   <si>
     <t xml:space="preserve">Radyo, sinema ve basın</t>
   </si>
   <si>
-    <t xml:space="preserve">Aynı mesajın radyo, film ve gazetede nasıl farklı karşılanabileceğini düşünün.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Üç mecra için birer avantaj ve birer sınır.</t>
+    <t xml:space="preserve">Aynı mesajın radyo, sinema ve gazetede nasıl farklı alımlanabileceğini değerlendiriniz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Üç mecranın her biri için bir avantaj ve bir sınırlılık.</t>
   </si>
   <si>
     <t xml:space="preserve">Smith–Mundt ve kurumlar</t>
   </si>
   <si>
-    <t xml:space="preserve">Yasal yetki, uygulama kapasitesi ve sonuç için ayrı kanıtlar belirleyin.</t>
+    <t xml:space="preserve">Yasal yetki, uygulama kapasitesi ve sonuç için ayrı kanıtlar belirleyiniz.</t>
   </si>
   <si>
     <t xml:space="preserve">Bir yasanın neyi mümkün kıldığı ve neyi tek başına kanıtlamadığı.</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">Ülkeler arası karşılaştırma</t>
   </si>
   <si>
-    <t xml:space="preserve">İki kültür kurumu veya yayıncıyı aynı üç soruyla karşılaştırın: kim yönetir, kime ulaşır, nasıl geri bildirim alır?</t>
+    <t xml:space="preserve">İki kültür kurumunu veya yayıncıyı yönetim, hedef kitle ve geri bildirim süreçleri bakımından karşılaştırınız.</t>
   </si>
   <si>
     <t xml:space="preserve">İki satırlık karşılaştırma ve sonucu etkileyebilecek bir bağlam farkı.</t>
@@ -185,31 +185,31 @@
     <t xml:space="preserve">Etkiyi değerlendirmek</t>
   </si>
   <si>
-    <t xml:space="preserve">3. sayfadaki sarı sayılardan birini değiştirin. Erişim ve destek değişimini ayrı okuyun.</t>
+    <t xml:space="preserve">3. sayfadaki sarı girdi hücrelerinden birini değiştiriniz. Erişimi ve destek değişimini ayrı ayrı yorumlayınız.</t>
   </si>
   <si>
     <t xml:space="preserve">Dört cümle: amaç, gözlem, başka açıklama ve ek kanıt ihtiyacı.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kendi cümleniz için şablon: “Bu kaynak … gösteriyor. … sonucuna ulaşmak için ayrıca … gerekir.”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Örnek: “Afiş, mesajın üretildiğini gösteriyor. İkna sonucuna ulaşmak için kitlenin tepkisini de bilmem gerekir.”</t>
+    <t xml:space="preserve">Analitik ifade şablonu: “Bu kaynak … göstermektedir. … sonucuna ulaşmak için ayrıca … kanıtı gereklidir.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Örnek: “Afiş, mesajın üretildiğini göstermektedir. İkna sonucuna ulaşmak için kitlenin tepkisine ilişkin kanıt da gereklidir.”</t>
   </si>
   <si>
     <t xml:space="preserve">Kaynak: Bu sitedeki 14 haftalık Türkçe ders notu. Bağlantılar yukarıdaki ilgili hafta satırındadır.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bir iddiayı kanıtla nasıl sınarım?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. “Ne söylüyorum?” sorusuna tek cümle yazın. 2. Elinizdeki belgeyi belirtin. 3. Belgenin sınırını yazın.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kanıt = iddiayı destekleyen iz. “Kanıt matrisi”, bu izleri aynı sorularla karşılaştırdığınız aşağıdaki tablodur.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gündelik örnek: Kafenin ilanını görmek, oradan kahve satın aldığınızı kanıtlamaz. Aradaki adımı ayrı gösterin.</t>
+    <t xml:space="preserve">İddiaların kanıt temelinde sınanması</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. İddiayı tek cümleyle ifade ediniz. 2. İncelenen belgeyi belirtiniz. 3. Belgenin kanıtlama sınırlarını açıklayınız.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kanıt, bir iddiayı destekleyen izdir. Aşağıdaki kanıt matrisi, bu izlerin ortak sorular temelinde karşılaştırılmasını sağlar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Açıklayıcı örnek: Kafe ilanıyla karşılaşılması, kahve satın alındığını göstermez. İki olay arasındaki eksik adımı belirleyiniz.</t>
   </si>
   <si>
     <t xml:space="preserve">Çözülmüş örnekler: Aşağıdaki belge türleri öğretim içindir. Bunlar bulunmuş gerçek arşiv belgeleri değildir.</t>
@@ -218,19 +218,19 @@
     <t xml:space="preserve">Örnek</t>
   </si>
   <si>
-    <t xml:space="preserve">Ne söylüyorum? (iddia)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neye bakıyorum? (belge türü)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belge neyi gösterebilir?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tek başına neyi göstermez?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Başka ne açıklayabilir?</t>
+    <t xml:space="preserve">Sınanan iddia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İncelenen belge türü</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belgenin gösterebileceği husus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tek başına gösteremeyeceği husus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olası rakip açıklama</t>
   </si>
   <si>
     <t xml:space="preserve">Ders bağlantısı</t>
@@ -290,22 +290,19 @@
     <t xml:space="preserve">Yerel yorumlar ve mevcut görüşler farklı olabilir.</t>
   </si>
   <si>
-    <t xml:space="preserve">Şimdi siz: Bir ders notundan olay seçin. Sarı satırı doldurun. Belgeyi görmediyseniz “aranacak belge” yazın.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vakam / haftam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ne söylüyorum?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belgem / arayacağım belge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bundan ne öğrenirim?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neyi hâlâ bilmiyorum?</t>
+    <t xml:space="preserve">Uygulama: Ders notundan bir vaka seçerek sarı satırı doldurunuz. İncelenmemiş belgeleri “aranacak belge” olarak belirtiniz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vaka / hafta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belge / aranacak belge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belgeden çıkarılabilecek bilgi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yanıtlanmamış sorular</t>
   </si>
   <si>
     <t xml:space="preserve">Başka açıklama</t>
@@ -326,28 +323,28 @@
     <t xml:space="preserve">Uygulama 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Kendinizi kontrol edin: “Belge var” mı dedim, “etki var” mı dedim? İkincisini yazdıysam aradaki yolu gösterebildim mi?</t>
+    <t xml:space="preserve">Değerlendirme: Belgenin varlığı ile etkiye ilişkin iddia ayrılmış mıdır? Etki iddiası varsa bağlantıyı kuran adımlar gösterilmiş midir?</t>
   </si>
   <si>
     <t xml:space="preserve">Örneklere temel: 6. hafta eğitim değişimi, 7. hafta CPI, 11. hafta medya. İlgili ders notları örnek satırlarında bağlıdır.</t>
   </si>
   <si>
-    <t xml:space="preserve">Erişim ile destek değişimini ayırın</t>
+    <t xml:space="preserve">Erişim ve destek değişiminin karşılaştırılması</t>
   </si>
   <si>
     <t xml:space="preserve">Tamamen varsayımsal veri: A ve B hayalî kampanyalardır. Sayılar gerçek kişi, öğrenci veya tarihsel olay verisi değildir.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Sarı hücrelere bakın. 2. Önce aşağıdaki çözülmüş örneği okuyun. 3. D10’u 600 yapıp sonuçları izleyin.</t>
+    <t xml:space="preserve">1. Sarı girdi hücrelerini inceleyiniz. 2. Aşağıdaki çözülmüş örneği okuyunuz. 3. D10’a 600 girerek sonuçlardaki değişimi gözlemleyiniz.</t>
   </si>
   <si>
     <t xml:space="preserve">Başlangıç örneğinde, her kampanyada ulaşılanlardan seçilmiş aynı 100 kişiye önce ve sonra aynı destek sorusu soruldu.</t>
   </si>
   <si>
-    <t xml:space="preserve">“Destek” = soruya olumlu yanıt. İkna için daha güçlü kanıt gerekir. Kontrol grubu olmayan bu gözlem neden-sonuç kanıtlamaz.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kontrol grubu = kampanyayı almayan, karşılaştırma için izlenen benzer kişiler. Bu örnekte böyle bir grup yok.</t>
+    <t xml:space="preserve">“Destek”, soruya verilen olumlu yanıttır. İkna iddiası daha güçlü kanıt gerektirir. Kontrol grubu bulunmayan bu gözlem nedenselliği kanıtlamaz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontrol grubu, kampanyaya maruz kalmayan ve karşılaştırma amacıyla izlenen benzer kişilerden oluşur. Bu örnekte kontrol grubu bulunmamaktadır.</t>
   </si>
   <si>
     <t xml:space="preserve">Kampanya</t>
@@ -392,10 +389,10 @@
     <t xml:space="preserve">Değişim (yüzde puan)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hesap nasıl yapılır?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sonucu nasıl okurum?</t>
+    <t xml:space="preserve">Hesaplama yöntemi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonucun yorumu</t>
   </si>
   <si>
     <t xml:space="preserve">Erişim = ulaşan ÷ hedef.</t>
@@ -407,22 +404,22 @@
     <t xml:space="preserve">Çözülmüş başlangıç örneği: A’da 800 ÷ 1.000 = %80 erişim. Destek %40’tan %44’e çıkar: 4 yüzde puan.</t>
   </si>
   <si>
-    <t xml:space="preserve">B’de başlangıç erişimi daha düşüktür (%40). Destek artışı daha büyüktür (15 yüzde puan). Görülmek ile ikna ayrı sorulardır.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alıştırma 1: D10’u 800’den 600’e değiştirin. Erişim %60 olur. Destek değişimi neden aynı kalır?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alıştırma 2: G10’u 44’ten 60’a değiştirin. Destek %60 olur ve artış 20 yüzde puana çıkar. Hangi veri değişti?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alıştırma 3: E10’u boş bırakın. Sonucun kaybolması neden %0 görünmesinden daha dürüsttür? Sonra 100 yazın.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alıştırma 4: “B daha çok ikna etti” demeden önce ne öğrenmelisiniz? Başlangıç farkları ve başka olayları düşünün.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cevabınız</t>
+    <t xml:space="preserve">B’de başlangıç erişimi daha düşük (%40), destek artışı daha yüksektir (15 yüzde puan). Maruz kalma ile ikna ayrı ayrı değerlendirilmelidir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alıştırma 1: D10’u 800’den 600’e değiştiriniz. Erişim %60 olur. Destek değişiminin neden sabit kaldığını açıklayınız.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alıştırma 2: G10’u 44’ten 60’a değiştiriniz. Destek %60, artış 20 yüzde puan olur. Değişen girdiyi belirleyiniz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alıştırma 3: E10’u boş bırakınız. Eksik veri için sonucun boş kalmasının neden %0 gösterilmesinden uygun olduğunu açıklayınız. Ardından 100 giriniz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alıştırma 4: B’nin daha fazla ikna sağladığı iddiası için gereken ek kanıtı belirtiniz. Başlangıç farklarını ve diğer olayları değerlendiriniz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yanıt</t>
   </si>
   <si>
     <t xml:space="preserve">Erişim neyi ölçer?</t>
@@ -437,16 +434,16 @@
     <t xml:space="preserve">Hangi ek veri gerekir?</t>
   </si>
   <si>
-    <t xml:space="preserve">Kararımın sınırı</t>
+    <t xml:space="preserve">Sonucun sınırlılığı</t>
   </si>
   <si>
     <t xml:space="preserve">Bir cümlelik sonuç</t>
   </si>
   <si>
-    <t xml:space="preserve">Benim açıklamam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Formülü görmek için C16’ya tıklayın. Üstteki formül çubuğunda D10/C10, yani “ulaşan kişi / hedef kişi” görünür.</t>
+    <t xml:space="preserve">Analitik açıklama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formülü incelemek için C16’yı seçiniz. Formül çubuğundaki D10/C10, “ulaşılan kişi sayısı / hedef kişi sayısı” oranını ifade eder.</t>
   </si>
   <si>
     <t xml:space="preserve">Yüzde puan: %40 ile %44 arasındaki fark 4 puandır. Göreli yüzde artışı ise %10’dur. Bunlar farklı ölçülerdir.</t>
@@ -455,31 +452,31 @@
     <t xml:space="preserve">Kaynak: Bu sayfadaki sayılar öğretim amacıyla kuruldu. Kavramlar dersin 1. ve 14. hafta notlarına dayanır.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kavramları günlük dille okuyun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Bilmediğiniz sözcüğü bulun. 2. Günlük örneği okuyun. 3. Son sütundaki soruyu seçtiğiniz ders vakasına uygulayın.</t>
+    <t xml:space="preserve">Temel kavramlar ve açıklayıcı benzetmeler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. İncelenecek kavramı belirleyiniz. 2. Açıklayıcı örneği okuyunuz. 3. Son sütundaki soruyu seçilen ders vakasına uygulayınız.</t>
   </si>
   <si>
     <t xml:space="preserve">Kavram</t>
   </si>
   <si>
-    <t xml:space="preserve">Kısaca anlamı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Günlük benzetme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kendinize sorun</t>
+    <t xml:space="preserve">Kısa tanım</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Açıklayıcı benzetme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analitik soru</t>
   </si>
   <si>
     <t xml:space="preserve">Aktör</t>
   </si>
   <si>
-    <t xml:space="preserve">Bir şey yapmaya çalışan kişi veya kuruluş.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kafe sahibi bir ilan hazırlatıyor.</t>
+    <t xml:space="preserve">Belirli bir amacı gerçekleştirmeye çalışan kişi veya kuruluş.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bir kafe sahibinin ilan hazırlatması.</t>
   </si>
   <si>
     <t xml:space="preserve">Kim, neyi değiştirmeye çalışıyor?</t>
@@ -494,7 +491,7 @@
     <t xml:space="preserve">Kafenin çevresindeki öğrenciler.</t>
   </si>
   <si>
-    <t xml:space="preserve">Hangi insanlar? Hepsini aynı mı sayıyorum?</t>
+    <t xml:space="preserve">Hangi gruplar incelenmektedir? Aralarındaki farklılıklar dikkate alınmış mıdır?</t>
   </si>
   <si>
     <t xml:space="preserve">Kaynak</t>
@@ -512,7 +509,7 @@
     <t xml:space="preserve">Araç</t>
   </si>
   <si>
-    <t xml:space="preserve">Kaynağın insanlarla temas etme biçimi.</t>
+    <t xml:space="preserve">Bir kaynağın insanlarla etkileşim kurmak için kullanılma biçimi.</t>
   </si>
   <si>
     <t xml:space="preserve">İlan, tanıtım etkinliği veya davet.</t>
@@ -524,19 +521,19 @@
     <t xml:space="preserve">Mekanizma</t>
   </si>
   <si>
-    <t xml:space="preserve">Bir şeyin başka bir şeyi nasıl değiştirebileceğini anlatan yol.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Güvenilir bir tavsiye, deneme isteği doğuruyor.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aradaki adım ne? Bu adımı gözleyebilir miyim?</t>
+    <t xml:space="preserve">Bir etkenin başka bir etkeni nasıl değiştirebileceğini açıklayan süreç.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Güvenilir bir tavsiyenin deneme isteğini artırması.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ara aşama nedir? Bu aşama gözlemlenebilir mi?</t>
   </si>
   <si>
     <t xml:space="preserve">Erişim</t>
   </si>
   <si>
-    <t xml:space="preserve">İnsanların içerikle karşılaşması. Tanımını ve sayım yöntemini belirtin.</t>
+    <t xml:space="preserve">İnsanların içerikle karşılaşması. Tanımın ve sayım yönteminin belirtilmesi gerekir.</t>
   </si>
   <si>
     <t xml:space="preserve">Kaç kişi ilanı gerçekten gördü?</t>
@@ -551,10 +548,10 @@
     <t xml:space="preserve">İnsanların mesajı nasıl anladığı ve değerlendirdiği.</t>
   </si>
   <si>
-    <t xml:space="preserve">Aynı ilanı biri faydalı, biri itici bulur.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kitle ne anlam çıkardı? Kendi sesini duyuyor muyum?</t>
+    <t xml:space="preserve">Aynı ilanın bir kişi tarafından yararlı, diğeri tarafından itici bulunması.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kitle mesajı nasıl yorumlamıştır? Kitlenin kendi ifadelerine ilişkin kanıt var mıdır?</t>
   </si>
   <si>
     <t xml:space="preserve">Tutum ve davranış</t>
@@ -566,7 +563,7 @@
     <t xml:space="preserve">Kafeyi sevmek tutum, alışveriş yapmak davranıştır.</t>
   </si>
   <si>
-    <t xml:space="preserve">Düşünce mi, eylem mi ölçüyorum?</t>
+    <t xml:space="preserve">Ölçülen unsur bir değerlendirme mi, gözlenebilir eylem mi?</t>
   </si>
   <si>
     <t xml:space="preserve">Sert güç</t>
@@ -590,7 +587,7 @@
     <t xml:space="preserve">Birini, iyi örnek olduğu için izlemek.</t>
   </si>
   <si>
-    <t xml:space="preserve">Hayranlığı politika desteğiyle karıştırıyor muyum?</t>
+    <t xml:space="preserve">Hayranlık ile politika desteği analitik olarak ayrılmış mıdır?</t>
   </si>
   <si>
     <t xml:space="preserve">Kamu diplomasisi</t>
@@ -626,7 +623,7 @@
     <t xml:space="preserve">Yanlışını açıkça düzelten bir konuşmacı.</t>
   </si>
   <si>
-    <t xml:space="preserve">İnanma nedenini nasıl biliyorum?</t>
+    <t xml:space="preserve">Kaynağa duyulan güvenin nedenleri hangi kanıta dayanmaktadır?</t>
   </si>
   <si>
     <t xml:space="preserve">Karşılıklılık</t>
@@ -674,7 +671,7 @@
     <t xml:space="preserve">800 ulaşan / 1.000 hedef = %80.</t>
   </si>
   <si>
-    <t xml:space="preserve">Aynı kitle ve dönemden sayıları mı bölüyorum?</t>
+    <t xml:space="preserve">Pay ve payda aynı kitleye ve döneme mi ilişkindir?</t>
   </si>
   <si>
     <t xml:space="preserve">Yüzde puan</t>
@@ -686,25 +683,25 @@
     <t xml:space="preserve">%40’tan %44’e geçiş 4 yüzde puandır.</t>
   </si>
   <si>
-    <t xml:space="preserve">Yüzde artışıyla karıştırıyor muyum?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaynak: Dersin Türkçe notlarındaki kavramsal açıklamalar. Günlük benzetmeler yalnızca öğrenmeyi kolaylaştıran örneklerdir.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Araştırma tasarımınızı adım adım kurun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Çözülmüş kurmaca örneği okuyun. 2. Sarı sütuna kendi vakanızı yazın. 3. İddianızı desteklemeyen kanıtı da arayın.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaynak kökeni, belgenin kim tarafından, ne zaman ve hangi amaçla üretildiğini ve size nasıl ulaştığını belirtir.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gözlem belgede bulunan şeydir. Yorum, bundan çıkardığınız anlamdır. İkisini ayrı yazmak çıkarımınızı denetlenebilir kılar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Örnek tamamen kurmacadır. ÖRNEK-1 gerçek bir belge kodu değildir. Sarı alanlara öğrenci adı veya kişisel veri yazmayın.</t>
+    <t xml:space="preserve">Yüzde puan ile göreli yüzde artışı ayrılmış mıdır?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaynak: Dersin Türkçe notlarındaki kavramsal açıklamalar. Açıklayıcı benzetmeler yalnızca öğrenmeyi kolaylaştıran örneklerdir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Araştırma tasarımının aşamaları</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Çözülmüş kurmaca örneği inceleyiniz. 2. Seçilen vakayı sarı sütunda açıklayınız. 3. İddiayla çelişebilecek kanıtları da araştırınız.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaynak kökeni, belgenin üreticisini, tarihini, amacını ve araştırmacıya hangi yolla ulaştığını belirtir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gözlem, belgede yer alan bilgidir. Yorum, bu bilgiden yapılan çıkarımdır. İkisinin ayrı belirtilmesi, çıkarımın denetlenmesini sağlar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Örnek tamamen kurmacadır. ÖRNEK-1 gerçek bir belge kodu değildir. Sarı alanlara öğrenci adı veya kişisel veri girmeyiniz.</t>
   </si>
   <si>
     <t xml:space="preserve">Kanıtı sorgulama alanı</t>
@@ -713,10 +710,10 @@
     <t xml:space="preserve">Çözülmüş kurmaca örnek</t>
   </si>
   <si>
-    <t xml:space="preserve">Sizin çalışmanız (doldurun)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">İddia: Sınadığım cümle</t>
+    <t xml:space="preserve">Araştırma uygulaması</t>
+  </si>
+  <si>
+    <t xml:space="preserve">İddia: Sınanacak önerme</t>
   </si>
   <si>
     <t xml:space="preserve">Değişim atölyesi, iki öğretmenin ilk ortak ders planını hazırlamasına katkıda bulundu. Bu, sınanacak iddiadır; henüz sonuç değildir.</t>
@@ -728,13 +725,13 @@
     <t xml:space="preserve">ÖRNEK-1: Katılımcı A’nın katılımcı B’ye atölye sonrasında yazdığı varsayılan özel mektup. Üretici, alıcı, tarih, amaç ve saklandığı yer gerçek araştırmada ayrıca doğrulanır.</t>
   </si>
   <si>
-    <t xml:space="preserve">Gözlem: Belgede tam olarak ne var?</t>
+    <t xml:space="preserve">Gözlem: Belgenin içerdiği bilgi</t>
   </si>
   <si>
     <t xml:space="preserve">Varsayılan mektup, ortak bir ders taslağından söz eder. Bu gözlem, mektubun içeriğine ilişkindir; taslağın uygulandığını göstermez.</t>
   </si>
   <si>
-    <t xml:space="preserve">Yorum: Bu gözlemden ne çıkarıyorum?</t>
+    <t xml:space="preserve">Yorum: Gözlemden yapılan çıkarım</t>
   </si>
   <si>
     <t xml:space="preserve">Atölye sonrasında iletişimin sürmüş olmasıyla uyumludur. Atölyenin tek neden olduğu veya ilişkinin kalıcı olduğu sonucuna yetmez.</t>
@@ -746,28 +743,28 @@
     <t xml:space="preserve">Öğretmenler önceden tanışıyor veya başka bir proje için zaten işbirliği planlıyor olabilir. Atölye öncesi yazışmalar bu açıklamayı sınayabilir.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sınırlılık: Kanıtımın sınırı nedir?</t>
+    <t xml:space="preserve">Sınırlılık: Kanıtın açıklama sınırı</t>
   </si>
   <si>
     <t xml:space="preserve">Tek bir öz bildirime dayanır. Yazışmanın seçilerek korunması, olumlu anlatım ve karşı tarafın sessizliği sonucu çarpıtabilir. İletişim, politika değişikliği anlamına gelmez.</t>
   </si>
   <si>
-    <t xml:space="preserve">Sonraki kanıt: Neyi kontrol edeceğim?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atölye öncesi kayıtları, ikinci katılımcının anlatısını ve tarihli ortak taslağı karşılaştırırım. Çelişki bulursam iddiayı daraltırım; aynı kaynağın tekrarını bağımsız doğrulama saymam.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Şimdi tasarım kararları: Her satır bir araştırma tercihini açık eder. Veri yoksa sonuç uydurmak yerine hangi veriyi arayacağınızı yazın.</t>
+    <t xml:space="preserve">Ek kanıt: Doğrulanacak hususlar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atölye öncesi kayıtlar, ikinci katılımcının anlatısı ve tarihli ortak taslak karşılaştırılır. Çelişki varsa iddia daraltılır. Aynı kaynağın tekrarı bağımsız doğrulama sayılmaz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tasarım kararları: Her satır bir araştırma tercihini açıklar. Veri bulunmuyorsa gerekli kanıtı belirtiniz ve sonuç iddiasını sınırlayınız.</t>
   </si>
   <si>
     <t xml:space="preserve">Tasarım kararı</t>
   </si>
   <si>
-    <t xml:space="preserve">Örnekte nasıl uygulanır?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benim araştırma planım</t>
+    <t xml:space="preserve">Örnekteki uygulama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Araştırma planı</t>
   </si>
   <si>
     <t xml:space="preserve">Araştırma sorusu</t>
@@ -779,19 +776,19 @@
     <t xml:space="preserve">İnceleme birimi</t>
   </si>
   <si>
-    <t xml:space="preserve">Bir öğretmen çifti ve onun ortak çalışma süreci. Kişi, etkinlik ve ülke düzeyindeki iddiaları birbirine karıştırmam.</t>
+    <t xml:space="preserve">Bir öğretmen çifti ve ortak çalışma süreci. Kişi, etkinlik ve ülke düzeyindeki iddialar analitik olarak ayrı tutulur.</t>
   </si>
   <si>
     <t xml:space="preserve">Zaman ve kapsam</t>
   </si>
   <si>
-    <t xml:space="preserve">Varsayımsal plan: atölyeden önceki ve sonraki üç ay. Bu sınırın dışındaki olayları ancak gerekçesini belirterek eklerim.</t>
+    <t xml:space="preserve">Varsayımsal plan: atölyeden önceki ve sonraki üç ay. Bu kapsamın dışındaki olaylar yalnızca açık bir gerekçeyle incelemeye eklenir.</t>
   </si>
   <si>
     <t xml:space="preserve">Beklenen mekanizma</t>
   </si>
   <si>
-    <t xml:space="preserve">Atölyede temas kurulması, ortak bir konu seçilmesi ve birlikte taslak hazırlanması. Her adım için ayrı bir iz ararım.</t>
+    <t xml:space="preserve">Atölyede temas kurulması, ortak bir konu seçilmesi ve birlikte taslak hazırlanması. Her aşama için ayrı bir gözlenebilir iz aranır.</t>
   </si>
   <si>
     <t xml:space="preserve">Gösterge ve tanımı</t>
@@ -803,28 +800,28 @@
     <t xml:space="preserve">Vaka seçimi</t>
   </si>
   <si>
-    <t xml:space="preserve">Yalnız başarı anlatılarını seçmem. Devam etmeyen temasları da arar, hangi kişilerin veya belgelerin neden dışarıda kaldığını kaydederim.</t>
+    <t xml:space="preserve">Vaka seçimi başarı anlatılarıyla sınırlanmaz. Sürmeyen temaslar da araştırılır. Kişi veya belgelerin dışarıda bırakılma nedenleri kaydedilir.</t>
   </si>
   <si>
     <t xml:space="preserve">Karşılaştırma ve karşı olgu</t>
   </si>
   <si>
-    <t xml:space="preserve">Atölye öncesindeki işbirliğini ve uygun benzer katılmayan kişileri araştırırım. Grupların başlangıçta farklı olabileceğini açıklarım; benzerliği otomatik varsaymam.</t>
+    <t xml:space="preserve">Atölye öncesindeki işbirliği ve karşılaştırmaya uygun katılmayan kişiler araştırılır. Grupların başlangıç farklılıkları açıklanır. Karşılaştırılabilirlik varsayılmaz.</t>
   </si>
   <si>
     <t xml:space="preserve">Etik ve veri yönetimi</t>
   </si>
   <si>
-    <t xml:space="preserve">Gönüllü katılım, uygun izin, kişisel bilgilerin azaltılması ve güvenli saklama planı kurarım. Öğrenci verilerini bu çalışma kitabına kopyalamam.</t>
+    <t xml:space="preserve">Gönüllü katılım, uygun izin, kişisel verilerin en aza indirilmesi ve güvenli saklama planlanır. Öğrenci verileri bu çalışma kitabına aktarılmaz.</t>
   </si>
   <si>
     <t xml:space="preserve">Kaynak gösterme ve denetim izi</t>
   </si>
   <si>
-    <t xml:space="preserve">Yazar, tarih, başlık, koleksiyon veya yayın, kayıt/sayfa ve erişim bilgisini kaydederim. Çeviri, eksik belge ve değişen yorum için kısa bir işlem günlüğü tutarım.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teslim öncesi: İddia, gözlem, yorum ve sınır ayrı mı? En güçlü rakip açıklamayı sınamak için hangi kanıt gerekiyor?</t>
+    <t xml:space="preserve">Yazar, tarih, başlık, koleksiyon veya yayın, kayıt/sayfa ve erişim bilgisi kaydedilir. Çeviri, eksik belge ve değişen yorum için kısa bir işlem günlüğü tutulur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teslim öncesi değerlendirme: İddia, gözlem, yorum ve sınırlılık ayrılmış mıdır? En güçlü rakip açıklamayı sınamak için hangi kanıt gereklidir?</t>
   </si>
   <si>
     <t xml:space="preserve">Ders dayanağı: 6. hafta değişimler, 14. hafta kanıt ve değerlendirme. Kurmaca örnek herhangi bir tarihsel sonuca kanıt oluşturmaz.</t>
@@ -1487,11 +1484,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="73527653"/>
-        <c:axId val="48016607"/>
+        <c:axId val="5306518"/>
+        <c:axId val="26188151"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="73527653"/>
+        <c:axId val="5306518"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1536,7 +1533,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48016607"/>
+        <c:crossAx val="26188151"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1544,7 +1541,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="48016607"/>
+        <c:axId val="26188151"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1589,7 +1586,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73527653"/>
+        <c:crossAx val="5306518"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2925,29 +2922,29 @@
         <v>89</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="E17" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="F17" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>95</v>
       </c>
       <c r="I17" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="74" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1"/>
       <c r="B18" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
@@ -2960,7 +2957,7 @@
     <row r="19" customFormat="false" ht="74" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1"/>
       <c r="B19" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -2973,7 +2970,7 @@
     <row r="20" customFormat="false" ht="74" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1"/>
       <c r="B20" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -2986,7 +2983,7 @@
     <row r="21" customFormat="false" ht="74" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1"/>
       <c r="B21" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
@@ -3010,7 +3007,7 @@
     <row r="23" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
       <c r="B23" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -3034,7 +3031,7 @@
     <row r="25" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1"/>
       <c r="B25" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
@@ -3109,7 +3106,7 @@
     <row r="2" customFormat="false" ht="31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -3133,7 +3130,7 @@
     <row r="4" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -3146,7 +3143,7 @@
     <row r="5" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -3159,7 +3156,7 @@
     <row r="6" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -3172,7 +3169,7 @@
     <row r="7" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -3185,7 +3182,7 @@
     <row r="8" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -3198,32 +3195,32 @@
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1"/>
       <c r="B9" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="H9" s="4" t="s">
         <v>113</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>114</v>
       </c>
       <c r="I9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="29" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1"/>
       <c r="B10" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C10" s="17" t="n">
         <v>1000</v>
@@ -3249,7 +3246,7 @@
     <row r="11" customFormat="false" ht="29" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1"/>
       <c r="B11" s="14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C11" s="18" t="n">
         <v>1000</v>
@@ -3286,7 +3283,7 @@
     <row r="13" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -3310,25 +3307,25 @@
     <row r="15" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1"/>
       <c r="B15" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="E15" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="H15" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>123</v>
       </c>
       <c r="I15" s="1"/>
     </row>
@@ -3355,7 +3352,7 @@
         <v>4</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H16" s="6" t="str">
         <f aca="false">IF(H10&lt;&gt;"Hazır",H10,"Destek değişimi: "&amp;TEXT(F16,"0.0")&amp;" yüzde puan. Nedeni henüz bilinmiyor.")</f>
@@ -3386,7 +3383,7 @@
         <v>15</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H17" s="14" t="str">
         <f aca="false">IF(H11&lt;&gt;"Hazır",H11,"Destek değişimi: "&amp;TEXT(F17,"0.0")&amp;" yüzde puan. Nedeni henüz bilinmiyor.")</f>
@@ -3408,7 +3405,7 @@
     <row r="19" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1"/>
       <c r="B19" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -3421,7 +3418,7 @@
     <row r="20" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1"/>
       <c r="B20" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -3599,7 +3596,7 @@
     <row r="36" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1"/>
       <c r="B36" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
@@ -3612,7 +3609,7 @@
     <row r="37" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1"/>
       <c r="B37" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
@@ -3625,7 +3622,7 @@
     <row r="38" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1"/>
       <c r="B38" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
@@ -3638,7 +3635,7 @@
     <row r="39" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1"/>
       <c r="B39" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
@@ -3662,32 +3659,32 @@
     <row r="41" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1"/>
       <c r="B41" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="D41" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="E41" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="F41" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F41" s="4" t="s">
+      <c r="G41" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="H41" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>138</v>
       </c>
       <c r="I41" s="1"/>
     </row>
     <row r="42" customFormat="false" ht="88" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1"/>
       <c r="B42" s="23" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C42" s="24"/>
       <c r="D42" s="24"/>
@@ -3722,7 +3719,7 @@
     <row r="45" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1"/>
       <c r="B45" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
@@ -3735,7 +3732,7 @@
     <row r="46" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1"/>
       <c r="B46" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
@@ -3759,7 +3756,7 @@
     <row r="48" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1"/>
       <c r="B48" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -3871,7 +3868,7 @@
     <row r="2" customFormat="false" ht="31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -3891,7 +3888,7 @@
     <row r="4" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -3911,16 +3908,16 @@
     <row r="6" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
       <c r="B6" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>148</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -3928,16 +3925,16 @@
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1"/>
       <c r="B7" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="6" t="s">
         <v>151</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>152</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -3945,16 +3942,16 @@
     <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1"/>
       <c r="B8" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="D8" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="10" t="s">
         <v>155</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>156</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -3962,16 +3959,16 @@
     <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1"/>
       <c r="B9" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="D9" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="E9" s="10" t="s">
         <v>159</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>160</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -3979,16 +3976,16 @@
     <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1"/>
       <c r="B10" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="D10" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="10" t="s">
         <v>163</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>164</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -3996,16 +3993,16 @@
     <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1"/>
       <c r="B11" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="D11" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="E11" s="10" t="s">
         <v>167</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>168</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -4013,16 +4010,16 @@
     <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1"/>
       <c r="B12" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="D12" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="E12" s="10" t="s">
         <v>171</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>172</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -4030,16 +4027,16 @@
     <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1"/>
       <c r="B13" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="D13" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="E13" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -4047,16 +4044,16 @@
     <row r="14" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1"/>
       <c r="B14" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="D14" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="E14" s="10" t="s">
         <v>179</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>180</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -4064,16 +4061,16 @@
     <row r="15" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1"/>
       <c r="B15" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="D15" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="E15" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -4081,16 +4078,16 @@
     <row r="16" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1"/>
       <c r="B16" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C16" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="D16" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="E16" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>188</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -4098,16 +4095,16 @@
     <row r="17" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1"/>
       <c r="B17" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C17" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="D17" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="10" t="s">
         <v>191</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>192</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -4115,16 +4112,16 @@
     <row r="18" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1"/>
       <c r="B18" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="D18" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="E18" s="10" t="s">
         <v>195</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>196</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -4132,16 +4129,16 @@
     <row r="19" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1"/>
       <c r="B19" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="D19" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="E19" s="10" t="s">
         <v>199</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>200</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -4149,16 +4146,16 @@
     <row r="20" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1"/>
       <c r="B20" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C20" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="D20" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="E20" s="10" t="s">
         <v>203</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>204</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -4166,16 +4163,16 @@
     <row r="21" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1"/>
       <c r="B21" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C21" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="D21" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="E21" s="10" t="s">
         <v>207</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>208</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -4183,16 +4180,16 @@
     <row r="22" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1"/>
       <c r="B22" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="D22" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="E22" s="10" t="s">
         <v>211</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>212</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -4200,16 +4197,16 @@
     <row r="23" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
       <c r="B23" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="D23" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="E23" s="10" t="s">
         <v>215</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>216</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -4217,16 +4214,16 @@
     <row r="24" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
       <c r="B24" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="D24" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="E24" s="14" t="s">
         <v>219</v>
-      </c>
-      <c r="E24" s="14" t="s">
-        <v>220</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -4252,7 +4249,7 @@
     <row r="27" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1"/>
       <c r="B27" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -4338,7 +4335,7 @@
     <row r="2" customFormat="false" ht="31" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1"/>
       <c r="B2" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -4354,7 +4351,7 @@
     <row r="4" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -4363,7 +4360,7 @@
     <row r="5" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -4372,7 +4369,7 @@
     <row r="6" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -4381,7 +4378,7 @@
     <row r="7" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -4397,23 +4394,23 @@
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1"/>
       <c r="B9" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>229</v>
       </c>
       <c r="E9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1"/>
       <c r="B10" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="1"/>
@@ -4421,10 +4418,10 @@
     <row r="11" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1"/>
       <c r="B11" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="1"/>
@@ -4432,10 +4429,10 @@
     <row r="12" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1"/>
       <c r="B12" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>234</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>235</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="1"/>
@@ -4443,10 +4440,10 @@
     <row r="13" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1"/>
       <c r="B13" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>236</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>237</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="1"/>
@@ -4454,10 +4451,10 @@
     <row r="14" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1"/>
       <c r="B14" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>238</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>239</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="1"/>
@@ -4465,10 +4462,10 @@
     <row r="15" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1"/>
       <c r="B15" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>240</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>241</v>
       </c>
       <c r="D15" s="12"/>
       <c r="E15" s="1"/>
@@ -4476,10 +4473,10 @@
     <row r="16" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1"/>
       <c r="B16" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>242</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>243</v>
       </c>
       <c r="D16" s="16"/>
       <c r="E16" s="1"/>
@@ -4494,7 +4491,7 @@
     <row r="18" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1"/>
       <c r="B18" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -4510,23 +4507,23 @@
     <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1"/>
       <c r="B20" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="D20" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>247</v>
       </c>
       <c r="E20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1"/>
       <c r="B21" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="1"/>
@@ -4534,10 +4531,10 @@
     <row r="22" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1"/>
       <c r="B22" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="C22" s="10" t="s">
         <v>250</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>251</v>
       </c>
       <c r="D22" s="12"/>
       <c r="E22" s="1"/>
@@ -4545,10 +4542,10 @@
     <row r="23" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1"/>
       <c r="B23" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="C23" s="10" t="s">
         <v>252</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>253</v>
       </c>
       <c r="D23" s="12"/>
       <c r="E23" s="1"/>
@@ -4556,10 +4553,10 @@
     <row r="24" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1"/>
       <c r="B24" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>254</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>255</v>
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="1"/>
@@ -4567,10 +4564,10 @@
     <row r="25" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1"/>
       <c r="B25" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="C25" s="10" t="s">
         <v>256</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>257</v>
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="1"/>
@@ -4578,10 +4575,10 @@
     <row r="26" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1"/>
       <c r="B26" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C26" s="10" t="s">
         <v>258</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>259</v>
       </c>
       <c r="D26" s="12"/>
       <c r="E26" s="1"/>
@@ -4589,10 +4586,10 @@
     <row r="27" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1"/>
       <c r="B27" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>260</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>261</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="1"/>
@@ -4600,10 +4597,10 @@
     <row r="28" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1"/>
       <c r="B28" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>262</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>263</v>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="1"/>
@@ -4611,10 +4608,10 @@
     <row r="29" customFormat="false" ht="76" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1"/>
       <c r="B29" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="C29" s="14" t="s">
         <v>264</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>265</v>
       </c>
       <c r="D29" s="16"/>
       <c r="E29" s="1"/>
@@ -4629,7 +4626,7 @@
     <row r="31" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1"/>
       <c r="B31" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -4638,7 +4635,7 @@
     <row r="32" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1"/>
       <c r="B32" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
